--- a/results/Threshold_Sweep.xlsx
+++ b/results/Threshold_Sweep.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>fpr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mcc</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>bal_acc</t>
         </is>
@@ -503,12 +513,18 @@
         <v>0.3309352517985611</v>
       </c>
       <c r="H2" t="n">
+        <v>0.5872340425531914</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4867724867724867</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.5027027027027027</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.3474348842136505</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.7086486486486487</v>
       </c>
     </row>
@@ -535,12 +551,18 @@
         <v>0.3359375</v>
       </c>
       <c r="H3" t="n">
+        <v>0.6085106382978723</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4831460674157304</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.4594594594594595</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.3291701703883622</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.7002702702702703</v>
       </c>
     </row>
@@ -567,12 +589,18 @@
         <v>0.3620689655172414</v>
       </c>
       <c r="H4" t="n">
+        <v>0.6510638297872341</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5060240963855421</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.3601812222962395</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -599,12 +627,18 @@
         <v>0.3867924528301887</v>
       </c>
       <c r="H5" t="n">
+        <v>0.6851063829787234</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.3513513513513514</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.3854521279987749</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.7343243243243243</v>
       </c>
     </row>
@@ -631,12 +665,18 @@
         <v>0.4175824175824176</v>
       </c>
       <c r="H6" t="n">
+        <v>0.723404255319149</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5390070921985816</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.2864864864864865</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.3978334554451879</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.7367567567567568</v>
       </c>
     </row>
@@ -663,12 +703,18 @@
         <v>0.4375</v>
       </c>
       <c r="H7" t="n">
+        <v>0.7446808510638298</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.2432432432432433</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.3944981803483625</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.7283783783783784</v>
       </c>
     </row>
@@ -695,12 +741,18 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="H8" t="n">
+        <v>0.7574468085106383</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5511811023622047</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.227027027027027</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.4124138910773641</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.7364864864864864</v>
       </c>
     </row>
@@ -727,12 +779,18 @@
         <v>0.4657534246575342</v>
       </c>
       <c r="H9" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5528455284552846</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.2108108108108108</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.4149539717496591</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.7345945945945946</v>
       </c>
     </row>
@@ -759,12 +817,18 @@
         <v>0.5151515151515151</v>
       </c>
       <c r="H10" t="n">
+        <v>0.7957446808510639</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.172972972972973</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.4617284726156182</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.7535135135135136</v>
       </c>
     </row>
@@ -791,12 +855,18 @@
         <v>0.5483870967741935</v>
       </c>
       <c r="H11" t="n">
+        <v>0.8127659574468085</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.1513513513513514</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.4909294624254812</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.7643243243243243</v>
       </c>
     </row>
@@ -823,12 +893,18 @@
         <v>0.5862068965517241</v>
       </c>
       <c r="H12" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.1297297297297297</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.5223315824882198</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.7751351351351352</v>
       </c>
     </row>
@@ -855,12 +931,18 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="H13" t="n">
+        <v>0.8212765957446808</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.1297297297297297</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.4901743744484093</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.7551351351351352</v>
       </c>
     </row>
@@ -887,12 +969,18 @@
         <v>0.6037735849056604</v>
       </c>
       <c r="H14" t="n">
+        <v>0.8340425531914893</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6213592233009708</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.1135135135135135</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.5155662336501872</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.7632432432432432</v>
       </c>
     </row>
@@ -919,12 +1007,18 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="H15" t="n">
+        <v>0.825531914893617</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.594059405940594</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.1135135135135135</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.4830005750930271</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.7432432432432432</v>
       </c>
     </row>
@@ -951,12 +1045,18 @@
         <v>0.58</v>
       </c>
       <c r="H16" t="n">
+        <v>0.8212765957446808</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.1135135135135135</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.4664864864864865</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.7332432432432432</v>
       </c>
     </row>
@@ -983,12 +1083,18 @@
         <v>0.5957446808510638</v>
       </c>
       <c r="H17" t="n">
+        <v>0.825531914893617</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5773195876288659</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.1027027027027027</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.4678877204190327</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.7286486486486488</v>
       </c>
     </row>
@@ -1015,12 +1121,18 @@
         <v>0.6363636363636364</v>
       </c>
       <c r="H18" t="n">
+        <v>0.8382978723404255</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5957446808510638</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.08648648648648649</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.4967755607723897</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.7367567567567568</v>
       </c>
     </row>
@@ -1047,12 +1159,18 @@
         <v>0.6511627906976745</v>
       </c>
       <c r="H19" t="n">
+        <v>0.8425531914893617</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6021505376344086</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.08108108108108109</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.5069300283422067</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.7394594594594595</v>
       </c>
     </row>
@@ -1079,12 +1197,18 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="H20" t="n">
+        <v>0.8382978723404255</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5869565217391305</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.08108108108108109</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.4902341131197147</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.7294594594594594</v>
       </c>
     </row>
@@ -1111,12 +1235,18 @@
         <v>0.6410256410256411</v>
       </c>
       <c r="H21" t="n">
+        <v>0.8340425531914893</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5617977528089888</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.07567567567567568</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.4667759328105938</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.7121621621621621</v>
       </c>
     </row>
@@ -1143,12 +1273,18 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="H22" t="n">
+        <v>0.8382978723404255</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5581395348837209</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.06486486486486487</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.4717181312842628</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.7075675675675676</v>
       </c>
     </row>
